--- a/The structure and semantics of the website/struktura_saita_ABS_SEO_updated.xlsx
+++ b/The structure and semantics of the website/struktura_saita_ABS_SEO_updated.xlsx
@@ -1462,15 +1462,57 @@
         <x:v>Объединенная страница специалиста: «автовышка» и «автогидроподъемник» относятся к одному специалисту; отдельная страница АГП не создается.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
+    <x:row r="18" ht="39.599998474121094" customHeight="1">
+      <x:c r="A18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>машинисты спецтехники</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Отбор мотористов цементировочного агрегата для объектов</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>моторист цементировочного агр</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>моторист цементировочного агрегата; подбор моториста цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Добавлено 22.10.2026. Запланировано. Частотности не проверены. Рабочий родитель; публикация после подготовки и приёмки.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="39.599998474121094" customHeight="1">
+      <x:c r="A19" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>машинисты спецтехники</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>Отбор слесарей по ремонту ДСТ для объектов</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>слесарь по ремонту дорожно-строительных машин и тракторов; подбор слесаря по ремонту дорожно-строительной техники и тракторов; найти слесаря по ремонту техники; подбор и найм слесаря по ремонту дорожно-строительной техники; слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>Добавлено 22.10.2026. Запланировано. Частотности не проверены. Рабочий родитель; публикация после подготовки и приёмки.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1657,6 +1699,126 @@
       </x:c>
       <x:c r="F11" s="28" t="str">
         <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" customHeight="1">
+      <x:c r="A12" s="92" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B12" s="28" t="str">
+        <x:v>Новые специальности</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="str">
+        <x:v>Решение пользователя от 22.10.2026</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="str">
+        <x:v>Две страницы, пункты 18а и 18б</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="str">
+        <x:v>Прямое указание</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32.400001525878906" customHeight="1">
+      <x:c r="A13" s="92" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B13" s="28" t="str">
+        <x:v>HEAAD</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="str">
+        <x:v>https://heaad.ru/poisk-i-podbor-personala/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="str">
+        <x:v>Подбор персонала, точная специальность</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="str">
+        <x:v>Источник формулировок, не частотности</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="32.400001525878906" customHeight="1">
+      <x:c r="A14" s="92" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B14" s="28" t="str">
+        <x:v>HEAAD</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="str">
+        <x:v>https://heaad.ru/poisk-i-podbor-personala/slesar-po-remontu-dorozhno-stroitelnoi-tekhniki-i-traktorov/</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="str">
+        <x:v>Подбор персонала, точная специальность</x:v>
+      </x:c>
+      <x:c r="F14" s="28" t="str">
+        <x:v>Источник формулировок, не частотности</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="32.400001525878906" customHeight="1">
+      <x:c r="A15" s="92" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="28" t="str">
+        <x:v>UP business</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="str">
+        <x:v>https://upinc.ru/podbor/avtoservis/slesar-remontu-dorozhno-stroitelnoj-tekhniki/</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="str">
+        <x:v>Подбор персонала, точная специальность</x:v>
+      </x:c>
+      <x:c r="F15" s="28" t="str">
+        <x:v>Источник формулировок, не частотности</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="97.19999694824219" customHeight="1">
+      <x:c r="A16" s="92" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B16" s="28" t="str">
+        <x:v>ММЦ ПЕРСОНАЛ</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="str">
+        <x:v>https://mmc-rspp.ru/m/staffleasing/view/%D0%BF%D0%BE%D0%B4%D0%B1%D0%BE%D1%80-%D0%BF%D0%B5%D1%80%D1%81%D0%BE%D0%BD%D0%B0%D0%BB%D0%B0-%D0%BD%D0%B0-%D0%B2%D0%B0%D0%BA%D0%B0%D0%BD%D1%81%D0%B8%D1%8E-%D1%81%D0%BB%D0%B5%D1%81%D0%B0%D1%80%D1%8C-%D0%BF%D0%BE-%D1%80%D0%B5%D0%BC%D0%BE%D0%BD%D1%82%D1%83-%D0%B4%D0%BE%D1%80%D0%BE%D0%B6%D0%BD%D0%BE-%D1%81%D1%82%D1%80%D0%BE%D0%B8%D1%82%D0%B5%D0%BB%D1%8C%D0%BD%D1%8B%D1%85-%D0%BC%D0%B0%D1%88%D0%B8%D0%BD-%D0%B8-%D1%82%D1%80%D0%B0%D0%BA%D1%82%D0%BE%D1%80%D0%BE%D0%B2-6-%D0%B9-%D1%80%D0%B0%D0%B7%D1%80%D1%8F%D0%B4</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="E16" s="28" t="str">
+        <x:v>Лизинг и предоставление персонала, точная специальность</x:v>
+      </x:c>
+      <x:c r="F16" s="28" t="str">
+        <x:v>Источник формулировок, не частотности</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="32.400001525878906" customHeight="1">
+      <x:c r="A17" s="92" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B17" s="28" t="str">
+        <x:v>Стафф-Б</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="str">
+        <x:v>https://staff-b.ru/msk/autstaffing/proizvodstvo/slesari</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="E17" s="28" t="str">
+        <x:v>Аутстаффинг, смежная широкая специальность</x:v>
+      </x:c>
+      <x:c r="F17" s="28" t="str">
+        <x:v>Источник формулировок, не частотности</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1845,6 +2007,92 @@
         <x:v>К утверждению</x:v>
       </x:c>
       <x:c r="G10" s="98" t="str"/>
+    </x:row>
+    <x:row r="11" ht="21.600000381469727" customHeight="1">
+      <x:c r="A11" s="98" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="98" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="C11" s="98" t="str">
+        <x:v>В исходном ядре отсутствует</x:v>
+      </x:c>
+      <x:c r="D11" s="98" t="str">
+        <x:v>Отдельная страница; источники и маски собраны</x:v>
+      </x:c>
+      <x:c r="E11" s="98" t="str">
+        <x:v>Пункт 18а</x:v>
+      </x:c>
+      <x:c r="F11" s="98" t="str">
+        <x:v>Добавлено в план</x:v>
+      </x:c>
+      <x:c r="G11" s="98" t="str">
+        <x:v>Пользователь подтвердил специальность</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21.600000381469727" customHeight="1">
+      <x:c r="A12" s="98" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="98" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="C12" s="98" t="str">
+        <x:v>В исходном ядре отсутствует</x:v>
+      </x:c>
+      <x:c r="D12" s="98" t="str">
+        <x:v>Отдельная страница; ДСТ раскрыть как дорожно-строительную технику</x:v>
+      </x:c>
+      <x:c r="E12" s="98" t="str">
+        <x:v>Пункт 18б</x:v>
+      </x:c>
+      <x:c r="F12" s="98" t="str">
+        <x:v>Добавлено в план</x:v>
+      </x:c>
+      <x:c r="G12" s="98" t="str">
+        <x:v>Прямое указание пользователя</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="21.600000381469727" customHeight="1">
+      <x:c r="A13" s="98" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" s="98" t="str">
+        <x:v>Размещение новых специальностей</x:v>
+      </x:c>
+      <x:c r="C13" s="98" t="str">
+        <x:v>Пока используется существующая ветка специалистов спецтехники</x:v>
+      </x:c>
+      <x:c r="D13" s="98" t="str">
+        <x:v>Не переименовывать категорию; уточнить место в меню перед интеграцией</x:v>
+      </x:c>
+      <x:c r="E13" s="98" t="str">
+        <x:v>Навигация</x:v>
+      </x:c>
+      <x:c r="F13" s="98" t="str">
+        <x:v>Рабочее решение</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="21.600000381469727" customHeight="1">
+      <x:c r="A14" s="98" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="98" t="str">
+        <x:v>Частотность новых кластеров</x:v>
+      </x:c>
+      <x:c r="C14" s="98" t="str">
+        <x:v>У конкурентов найдены формулировки, спрос не измерен</x:v>
+      </x:c>
+      <x:c r="D14" s="98" t="str">
+        <x:v>Проверить частотности отдельно; не записывать нули</x:v>
+      </x:c>
+      <x:c r="E14" s="98" t="str">
+        <x:v>Обе новые страницы</x:v>
+      </x:c>
+      <x:c r="F14" s="98" t="str">
+        <x:v>Не проверена</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2236,11 +2484,33 @@
         <x:v>/mashinisty-spetstehniki/mashinist-avtovyshki/</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26.399999618530273" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>Главная</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>машинисты спецтехники</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>Главная</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>машинисты спецтехники</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2677,12 +2947,39 @@
         <x:v>машинист автовышки; оператор автовышки; машинист автогидроподъемника; оператор автогидроподъемника; машинист автовышки и автогидроподъемника</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
+    <x:row r="18" ht="26.399999618530273" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>моторист цементировочного агр</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Дочерняя, план</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>моторист цементировочного агрегата; подбор моториста цементировочного агрегата</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="39.599998474121094" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Дочерняя, план</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str">
+        <x:v>слесарь по ремонту дорожно-строительных машин и тракторов; подбор слесаря по ремонту дорожно-строительной техники и тракторов; найти слесаря по ремонту техники; подбор и найм слесаря по ремонту дорожно-строительной техники; слесарь по ремонту ДСТ</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2733,11 +3030,11 @@
         <x:v>Всего федеральных страниц</x:v>
       </x:c>
       <x:c r="B5" s="33" t="n">
-        <x:f>COUNTA('Паспорт структуры'!A5:A20)</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTA('Паспорт структуры'!A5:A22)</x:f>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="54" t="str">
-        <x:v>Таблица структуры, графическая карта и семантическое ядро подтверждают одно дерево: главная + 2 категории + 13 страниц специалистов. URL из дорожной карты приняты как эталонные. Все 16 H1 проверены и приведены к человекопонятным формулировкам с корректными склонениями. «Автовышка» и «автогидроподъемник» объединены в одну страницу, поэтому риск каннибализации снят. Коммерческий интент — B2B-подбор персонала для компаний; запросы о вакансиях, работе и резюме исключаются. До утверждения остается окончательное подтверждение группового формата заявок.</x:v>
+        <x:v>Исходная SEO-структура расширена до 18 страниц: главная, 2 категории и 15 специалистов. Две новые страницы добавлены по решению пользователя 22.10.2026. Формулировки конкурентов сохранены отдельно от масок; частотности не проверены. Добавление в план не означает готовность к публикации.</x:v>
       </x:c>
       <x:c r="E5" s="55"/>
       <x:c r="F5" s="55"/>
@@ -2749,7 +3046,7 @@
         <x:v>Страниц уровня 1</x:v>
       </x:c>
       <x:c r="B6" s="34" t="n">
-        <x:f>COUNTIF('Паспорт структуры'!B5:B20,1)</x:f>
+        <x:f>COUNTIF('Паспорт структуры'!B5:B22,1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="57"/>
@@ -2763,7 +3060,7 @@
         <x:v>Страниц уровня 2</x:v>
       </x:c>
       <x:c r="B7" s="34" t="n">
-        <x:f>COUNTIF('Паспорт структуры'!B5:B20,2)</x:f>
+        <x:f>COUNTIF('Паспорт структуры'!B5:B22,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="57"/>
@@ -2777,8 +3074,8 @@
         <x:v>Страниц уровня 3</x:v>
       </x:c>
       <x:c r="B8" s="34" t="n">
-        <x:f>COUNTIF('Паспорт структуры'!B5:B20,3)</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIF('Паспорт структуры'!B5:B22,3)</x:f>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="57"/>
       <x:c r="E8" s="58"/>
@@ -2791,7 +3088,7 @@
         <x:v>Высоких рисков каннибализации</x:v>
       </x:c>
       <x:c r="B9" s="34" t="n">
-        <x:f>COUNTIF('Паспорт структуры'!L5:L20,"Высокий")</x:f>
+        <x:f>COUNTIF('Паспорт структуры'!L5:L22,"Высокий")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="60"/>
@@ -2814,10 +3111,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="82" t="str">
-        <x:v>1. Все 16 страниц имеют URL и кластер — выполнено.
-2. Пересечения интентов описаны и получили правила разведения — выполнено.
-3. Региональные страницы не создавались — выполнено.
-4. Требуется прямое утверждение пользователя — ожидается.</x:v>
+        <x:v>Два новых URL и кластера добавлены 22.10.2026. Тексты, проверка частотностей, вёрстка и приёмка этих страниц впереди. Прежние статусы остальных страниц не пересматривались.</x:v>
       </x:c>
       <x:c r="B12" s="83"/>
       <x:c r="C12" s="83"/>
@@ -2897,7 +3191,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="16" t="str">
-        <x:v>16 страниц. Canonical URL взяты из дорожной карты и исходной структуры; региональные копии на этом этапе не создаются.</x:v>
+        <x:v>18 страниц SEO-структуры: 16 исходных и 2 новые запланированные. Региональные копии не создаются.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
@@ -3648,21 +3942,93 @@
         <x:v>На согласовании</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="62" customHeight="1">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-      <x:c r="I21"/>
-      <x:c r="J21"/>
-      <x:c r="K21"/>
-      <x:c r="L21"/>
-      <x:c r="M21"/>
-      <x:c r="N21"/>
+    <x:row r="21" ht="32.400001525878906" customHeight="1">
+      <x:c r="A21" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Специалист</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>/mashinisty-spetstehniki/</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Отбор мотористов цементировочного агрегата для объектов</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Отбор мотористов цементировочного агрегата для объектов</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>моторист цементировочного агр</x:v>
+      </x:c>
+      <x:c r="J21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>Предоставление мотористов цементировочного агрегата компаниям</x:v>
+      </x:c>
+      <x:c r="L21" t="str">
+        <x:v>Частотность не проверена</x:v>
+      </x:c>
+      <x:c r="M21" t="str">
+        <x:v>Специалист</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>Запланирована 22.10.2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="32.400001525878906" customHeight="1">
+      <x:c r="A22" s="92" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" s="92" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" s="92" t="str">
+        <x:v>Специалист</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="str">
+        <x:v>Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="F22" s="28" t="str">
+        <x:v>/mashinisty-spetstehniki/</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="str">
+        <x:v>Отбор слесарей по ремонту ДСТ для объектов</x:v>
+      </x:c>
+      <x:c r="H22" s="28" t="str">
+        <x:v>Отбор слесарей по ремонту ДСТ для объектов</x:v>
+      </x:c>
+      <x:c r="I22" s="28" t="str">
+        <x:v>слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="J22" s="92" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K22" s="28" t="str">
+        <x:v>Предоставление слесарей по ремонту дорожно-строительной техники компаниям</x:v>
+      </x:c>
+      <x:c r="L22" s="92" t="str">
+        <x:v>Частотность не проверена</x:v>
+      </x:c>
+      <x:c r="M22" s="92" t="str">
+        <x:v>Специалист</x:v>
+      </x:c>
+      <x:c r="N22" s="92" t="str">
+        <x:v>Запланирована 22.10.2026</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4045,13 +4411,45 @@
         <x:v>Автовышка и АГП — один специалист и один URL; оба термина раскрываются на объединенной странице.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="72" customHeight="1">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
+    <x:row r="21" ht="54" customHeight="1">
+      <x:c r="A21" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>отбор мотористов цементировочного агрегата; аутстаффинг мотористов цементировочного агрегата; предоставление мотористов цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Регион, график, тип техники и профиль работ</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>вакансия; работа; зарплата; резюме; обучение; курсы; удостоверение купить; продажа агрегата; аренда техники без персонала; ремонт техники как услуга</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Тип агрегата и задачи, опыт кандидата, документы, регион, график и дата выхода. Не приравнивать цементирование скважин к обычным строительным работам.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" s="28" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="str">
+        <x:v>отбор слесарей по ремонту ДСТ; аутстаффинг слесарей по ремонту ДСТ; предоставление слесарей по ремонту спецтехники</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="str">
+        <x:v>Регион, график, тип техники и профиль работ</x:v>
+      </x:c>
+      <x:c r="E22" s="94" t="str">
+        <x:v>вакансия; работа; зарплата; резюме; обучение; курсы; удостоверение купить; продажа агрегата; аренда техники без персонала; ремонт техники как услуга</x:v>
+      </x:c>
+      <x:c r="F22" s="96" t="str">
+        <x:v>Раскрыть ДСТ как дорожно-строительную технику. Уточнять тип машин, узлы и характер ремонта, опыт, документы и условия выхода. Продаём предоставление сотрудника, не ремонт техники как подряд.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4361,7 +4759,9 @@
 /mashinisty-spetstehniki/mashinist-truboukladchika/
 /mashinisty-spetstehniki/ekskavatorschik/
 /mashinisty-spetstehniki/mashinisty-avtokrana/
-/mashinisty-spetstehniki/mashinist-avtovyshki/</x:v>
+/mashinisty-spetstehniki/mashinist-avtovyshki/
+/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/
+/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
       </x:c>
       <x:c r="E15" s="28" t="str">
         <x:v>Главная &gt; Машинисты спецтехники</x:v>
@@ -4488,14 +4888,51 @@
         <x:v>Главная (карточка); категория; соседние услуги</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="82" customHeight="1">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
+    <x:row r="21" ht="21.600000381469727" customHeight="1">
+      <x:c r="A21" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>/mashinisty-spetstehniki/</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Главная &gt; Машинисты спецтехники &gt; Моторист цементировочного агрегата</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Родитель; главная; заявка; 2–4 релевантных соседа</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Карточка категории; каталог главной; меню после готовности</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="21.600000381469727" customHeight="1">
+      <x:c r="A22" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" s="28" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="str">
+        <x:v>/mashinisty-spetstehniki/</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="str">
+        <x:v>Главная &gt; Машинисты спецтехники &gt; Слесарь по ремонту ДСТ</x:v>
+      </x:c>
+      <x:c r="F22" s="28" t="str">
+        <x:v>Родитель; главная; заявка; 2–4 релевантных соседа</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="str">
+        <x:v>Карточка категории; каталог главной; меню после готовности</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5051,12 +5488,39 @@
         <x:v>Только шаблон</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
+    <x:row r="21" ht="21.600000381469727" customHeight="1">
+      <x:c r="A21" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>/{region-slug}/mashinisty-spetstehniki/motorist-tsementirovochnogo-agregata/</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Self-canonical после запуска регионов</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Только шаблон; не генерировать</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="21.600000381469727" customHeight="1">
+      <x:c r="A22" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" s="28" t="str">
+        <x:v>/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="C22" s="98" t="str">
+        <x:v>/{region-slug}/mashinisty-spetstehniki/slesar-po-remontu-dst/</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="str">
+        <x:v>Self-canonical после запуска регионов</x:v>
+      </x:c>
+      <x:c r="E22" s="96" t="str">
+        <x:v>Только шаблон; не генерировать</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
